--- a/koha_sql_cleanup.xlsx
+++ b/koha_sql_cleanup.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\nextkansas.sql\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\nextkansas.sql\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ECA6FBA-AD4D-480A-AF17-8B8BBE909C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE7CE234-B05D-45AB-AAB6-A280031A4956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3302" uniqueCount="2521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3304" uniqueCount="2521">
   <si>
     <t>ID</t>
   </si>
@@ -7608,12 +7608,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -7628,10 +7634,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7948,15 +7956,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I983"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" customWidth="1"/>
     <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="37.85546875" customWidth="1"/>
-    <col min="4" max="4" width="47.28515625" customWidth="1"/>
-    <col min="5" max="5" width="54" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="37.88671875" customWidth="1"/>
+    <col min="4" max="4" width="47.33203125" customWidth="1"/>
+    <col min="5" max="5" width="54" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" customWidth="1"/>
+    <col min="7" max="7" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -18113,7 +18121,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="641" spans="1:8">
+    <row r="641" spans="1:9">
       <c r="A641" s="2">
         <v>3550</v>
       </c>
@@ -18124,7 +18132,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="642" spans="1:8">
+    <row r="642" spans="1:9">
       <c r="A642" s="2">
         <v>3551</v>
       </c>
@@ -18138,24 +18146,32 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="643" spans="1:8">
-      <c r="A643" s="2">
+    <row r="643" spans="1:9">
+      <c r="A643" s="3">
         <v>3552</v>
       </c>
-      <c r="B643" t="s">
+      <c r="B643" s="4" t="s">
         <v>1731</v>
       </c>
-      <c r="C643" t="s">
+      <c r="C643" s="4" t="s">
         <v>1483</v>
       </c>
+      <c r="D643" s="4"/>
       <c r="E643" t="s">
         <v>1732</v>
       </c>
-      <c r="F643" t="s">
+      <c r="F643" s="4" t="s">
         <v>1484</v>
       </c>
-    </row>
-    <row r="644" spans="1:8">
+      <c r="G643" s="4"/>
+      <c r="H643" s="4" t="s">
+        <v>2518</v>
+      </c>
+      <c r="I643" s="4" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="644" spans="1:9">
       <c r="A644" s="2">
         <v>3556</v>
       </c>
@@ -18166,7 +18182,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="645" spans="1:8">
+    <row r="645" spans="1:9">
       <c r="A645" s="2">
         <v>3557</v>
       </c>
@@ -18180,7 +18196,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="646" spans="1:8">
+    <row r="646" spans="1:9">
       <c r="A646" s="2">
         <v>3558</v>
       </c>
@@ -18194,7 +18210,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="647" spans="1:8">
+    <row r="647" spans="1:9">
       <c r="A647" s="2">
         <v>3559</v>
       </c>
@@ -18211,7 +18227,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="648" spans="1:8">
+    <row r="648" spans="1:9">
       <c r="A648" s="2">
         <v>3570</v>
       </c>
@@ -18225,7 +18241,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="649" spans="1:8">
+    <row r="649" spans="1:9">
       <c r="A649" s="2">
         <v>3572</v>
       </c>
@@ -18245,7 +18261,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="650" spans="1:8">
+    <row r="650" spans="1:9">
       <c r="A650" s="2">
         <v>3577</v>
       </c>
@@ -18265,7 +18281,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="651" spans="1:8">
+    <row r="651" spans="1:9">
       <c r="A651" s="2">
         <v>3578</v>
       </c>
@@ -18285,7 +18301,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="652" spans="1:8">
+    <row r="652" spans="1:9">
       <c r="A652" s="2">
         <v>3579</v>
       </c>
@@ -18305,7 +18321,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="653" spans="1:8">
+    <row r="653" spans="1:9">
       <c r="A653" s="2">
         <v>3580</v>
       </c>
@@ -18325,7 +18341,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="654" spans="1:8">
+    <row r="654" spans="1:9">
       <c r="A654" s="2">
         <v>3581</v>
       </c>
@@ -18345,7 +18361,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="655" spans="1:8">
+    <row r="655" spans="1:9">
       <c r="A655" s="2">
         <v>3582</v>
       </c>
@@ -18365,7 +18381,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="656" spans="1:8">
+    <row r="656" spans="1:9">
       <c r="A656" s="2">
         <v>3583</v>
       </c>
